--- a/docs/検証報告書.xlsx
+++ b/docs/検証報告書.xlsx
@@ -8,18 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="1. 検証サマリ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2. 検証の観点" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3. 検証項目と結果" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4. 検出事項と対処" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5. 残課題" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2. 観点【正常系】" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3. 項目【正常系】" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4. 観点【異常系】" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4-2. 項目【異常系】" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. 検出事項と対処" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6. 再実行の手順" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7. 残課題" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'1. 検証サマリ'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'2. 検証の観点'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'3. 検証項目と結果'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'4. 検出事項と対処'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'5. 残課題'!$3:$3</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -27,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,14 +72,8 @@
       <color rgb="00B3261E"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Meiryo"/>
-      <b val="1"/>
-      <color rgb="00B26A00"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -102,6 +93,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F0E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A4F7A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6EEF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B3261E"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,13 +137,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -161,13 +167,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -175,25 +181,28 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -568,9 +577,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="76" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -595,7 +604,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>本システムを社内へ公開して差し支えないことを、根拠をもって示すこと。具体的には、①予約が二重に成立しないこと、②利用者が説明なしに操作できること、③管理者が専任を置かずに運用できること、④外部サービス（カレンダー・メール・LINE）との連携が実環境で成立すること、の4点を確認する。</t>
+          <t>本システムを社内へ公開して差し支えないことを、根拠をもって示すこと。①予約が二重に成立しないこと、②利用者が説明なしに操作できること、③管理者が専任を置かずに運用できること、④外部サービスとの連携が実環境で成立すること、⑤想定外の事態で業務が止まらないこと、の5点を確認する。</t>
         </is>
       </c>
     </row>
@@ -623,51 +632,51 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="53" customHeight="1">
+    <row r="7" ht="68" customHeight="1">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>検証の方式</t>
+          <t>検証の分け方</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>自動テスト（コードによる網羅検証）と、実機検証（外部サービスとの連携）の2本立て。自動テストは何度でも再実行でき、仕様変更時の再検証にそのまま使える。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="53" customHeight="1">
+          <t>【正常系】要件を満たしているかの検証。要件定義書の記述が根拠。　　　　　【異常系】運用上のリスクを想定した検証。要件には書かれていない壊れ方が対象。この2つを混ぜると、要件どおりに作れているのか、壊れにくく作れているのか、どちらが不足しているのか判断できなくなる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="23" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>実施した検証</t>
+          <t>正常系</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>自動テスト 212項目（予約ロジック・会話フロー・シート編集）／自動診断 33項目（構成・データ整合）／実機検証 7項目（外部連携・表示）。合計 252項目。すべて合格。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1">
+          <t>8観点 / 44項目。すべて合格。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="23" customHeight="1">
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>検証項目への整理</t>
+          <t>異常系</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>これらを45の検証項目に整理し、9つの観点に割り当てている。観点に属さない検証項目はなく、検証項目を持たない観点もない。</t>
+          <t>8観点 / 34項目。すべて合格。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>再検証の可否</t>
+          <t>検証の方式</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>自動テストと自動診断（245項目）は、エディタから何度でも再実行できる。仕様変更時の再検証にそのまま使える。</t>
+          <t>自動テスト7本と実機検証。自動テストはエディタから何度でも再実行でき、仕様変更時の再検証にそのまま使える（「6. 再実行の手順」を参照）。</t>
         </is>
       </c>
     </row>
@@ -679,7 +688,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>実装・検証の過程で7件を検出し、すべて修正済み。詳細は「4. 検出事項と対処」を参照。</t>
+          <t>13件を検出。うち重大2件・中8件・軽微2件は修正済み、1件は運用ルールで回避（システムでは防げないため）。</t>
         </is>
       </c>
     </row>
@@ -691,7 +700,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>3件。いずれもリリース可否に影響しない。詳細は「5. 残課題」を参照。</t>
+          <t>3件。いずれもリリース可否に影響しない。</t>
         </is>
       </c>
     </row>
@@ -705,7 +714,7 @@
     <row r="15" ht="42" customHeight="1">
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>設定した4つの目的すべてについて、対応する検証項目が合格している。未合格の項目はない。残課題3件は、いずれも発生しても予約の成立に影響せず、運用しながら確認できる性質のものである。</t>
+          <t>正常系・異常系のすべての観点に検証項目が割り当てられ、未合格の項目はない。検出した不具合は、システムで防げない1件を除きすべて修正済みである。残課題3件は、発生しても予約の成立に影響せず、運用しながら確認できる。</t>
         </is>
       </c>
     </row>
@@ -717,7 +726,7 @@
     <mergeCell ref="B15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -727,12 +736,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -740,14 +749,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>検証の観点</t>
+          <t>検証の観点【正常系】— 要件を満たしているか</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>「どこが壊れると事業に影響するか」から観点を立て、そこに検証項目を割り当てている。</t>
+          <t>要件定義書に書かれたことが根拠。「要件が実現されているか」を確かめる。</t>
         </is>
       </c>
     </row>
@@ -779,7 +788,7 @@
       </c>
     </row>
     <row r="4" ht="46" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -804,7 +813,7 @@
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -829,7 +838,7 @@
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -845,7 +854,7 @@
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
@@ -854,7 +863,7 @@
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -879,7 +888,7 @@
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>E</t>
         </is>
@@ -904,7 +913,7 @@
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -929,7 +938,7 @@
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>G</t>
         </is>
@@ -954,14 +963,14 @@
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>データが壊れないこと</t>
+          <t>データが正しい形式で保持されること</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -978,43 +987,18 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>想定外の操作に耐えること</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>古いメッセージのボタンを押す、無関係な文字を送る、通信が重複するなど、実運用で必ず起きる状況で破綻しないこと。</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="14" t="inlineStr"/>
-      <c r="B13" s="14" t="inlineStr">
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="14" t="inlineStr"/>
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr"/>
-      <c r="D13" s="15" t="n">
-        <v>45</v>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr"/>
+      <c r="D12" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>合格</t>
         </is>
@@ -1026,7 +1010,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1036,27 +1020,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>検証項目と結果</t>
+          <t>検証項目と結果【正常系】</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>各項目は「2. 検証の観点」のいずれかに属する。観点に属さない検証項目はなく、検証項目を持たない観点もない。</t>
+          <t>各項目は観点のいずれかに属する。観点に属さない項目はなく、項目を持たない観点もない。</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1071,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="10" t="n">
         <v>1</v>
       </c>
@@ -1103,7 +1087,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。同じ枠に対する2件目の予約を試み、拒否されることを確認</t>
+          <t>自動テスト（予約）</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -1112,7 +1096,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="12" t="n">
         <v>2</v>
       </c>
@@ -1128,7 +1112,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。10:00-11:00 の直後 11:00-12:00 が取れることを確認</t>
+          <t>自動テスト（予約）</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -1137,7 +1121,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="26" customHeight="1">
       <c r="A6" s="10" t="n">
         <v>3</v>
       </c>
@@ -1153,7 +1137,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。排他ロックの内側で判定と書き込みが行われることを確認</t>
+          <t>自動テスト（予約）</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -1162,7 +1146,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="12" t="n">
         <v>4</v>
       </c>
@@ -1178,7 +1162,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。書き込み直後に読み直し、同じ内容が得られることを確認</t>
+          <t>自動テスト（予約）</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -1187,7 +1171,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="10" t="n">
         <v>5</v>
       </c>
@@ -1203,7 +1187,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。曜日別の稼働設定に対して境界値を含めて確認</t>
+          <t>自動テスト（空き判定）</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -1212,7 +1196,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="12" t="n">
         <v>6</v>
       </c>
@@ -1228,7 +1212,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。部屋別の予約可能時間の区間外を確認</t>
+          <t>自動テスト（空き判定）</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -1237,7 +1221,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="26" customHeight="1">
       <c r="A10" s="10" t="n">
         <v>7</v>
       </c>
@@ -1253,7 +1237,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。全部屋指定・特定部屋指定の両方を確認</t>
+          <t>自動テスト（空き判定）</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1262,7 +1246,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" s="12" t="n">
         <v>8</v>
       </c>
@@ -1278,7 +1262,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。定員未満・定員ちょうど・定員超過の3通りを確認</t>
+          <t>自動テスト（空き判定）</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -1287,7 +1271,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="26" customHeight="1">
       <c r="A12" s="10" t="n">
         <v>9</v>
       </c>
@@ -1303,7 +1287,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。大部屋が少人数に占有されないことを確認</t>
+          <t>自動テスト（空き判定）</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -1312,7 +1296,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="26" customHeight="1">
       <c r="A13" s="12" t="n">
         <v>10</v>
       </c>
@@ -1323,12 +1307,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>開始時刻を過ぎた枠が予約できないこと</t>
+          <t>開始時刻を過ぎた枠が予約・変更・キャンセルできないこと</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。過去日時に対する予約・変更・キャンセルを確認</t>
+          <t>自動テスト（予約）</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -1337,7 +1321,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="26" customHeight="1">
       <c r="A14" s="10" t="n">
         <v>11</v>
       </c>
@@ -1348,12 +1332,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>予約可能日数（60日）を超える予約ができないこと</t>
+          <t>予約可能日数を超える予約ができないこと</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。境界値で確認</t>
+          <t>自動テスト（空き判定）</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -1362,7 +1346,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" ht="26" customHeight="1">
       <c r="A15" s="12" t="n">
         <v>12</v>
       </c>
@@ -1373,12 +1357,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>選択肢が設定値から生成されること</t>
+          <t>選択肢が設定値と部屋マスタから生成されること</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。設定を変えると選択肢が追従することを確認</t>
+          <t>自動テスト（空き判定）</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -1387,7 +1371,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="26" customHeight="1">
       <c r="A16" s="10" t="n">
         <v>13</v>
       </c>
@@ -1403,7 +1387,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。会話をイベント単位で再現し、応答内容を検証</t>
+          <t>自動テスト（会話）</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -1412,7 +1396,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="26" customHeight="1">
       <c r="A17" s="12" t="n">
         <v>14</v>
       </c>
@@ -1423,12 +1407,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>予約フロー全体が最後まで通ること</t>
+          <t>登録が必須であること・残りの手順が案内されること</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。日付〜確定までの全手順を通して実行し、予約の成立を確認</t>
+          <t>自動テスト（会話）</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -1437,7 +1421,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="26" customHeight="1">
       <c r="A18" s="10" t="n">
         <v>15</v>
       </c>
@@ -1448,12 +1432,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>予約の確認・変更・キャンセルができること</t>
+          <t>登録情報の変更手段が、登録直後と使い方の両方から辿れること</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。一覧表示から各操作までを通して実行</t>
+          <t>自動テスト（会話）</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -1462,7 +1446,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="26" customHeight="1">
       <c r="A19" s="12" t="n">
         <v>16</v>
       </c>
@@ -1473,12 +1457,12 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>空き状況が3状態（予約済み／予約不可／空き）で表示されること</t>
+          <t>予約フロー全体が最後まで通ること</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。予約・定例枠・空きが区別されることを確認</t>
+          <t>自動テスト（会話）</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -1487,7 +1471,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="26" customHeight="1">
       <c r="A20" s="10" t="n">
         <v>17</v>
       </c>
@@ -1498,12 +1482,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>登録情報の変更ができ、既存予約に反映されること</t>
+          <t>すべての手順から途中で離脱できること</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。氏名変更が予約者名と予約名に波及することを確認</t>
+          <t>自動テスト（会話）</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -1512,7 +1496,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="21" ht="26" customHeight="1">
       <c r="A21" s="12" t="n">
         <v>18</v>
       </c>
@@ -1523,12 +1507,12 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>日時・時間・部屋の指定がすべてボタン操作で完結すること</t>
+          <t>予約の確認・変更・キャンセルができること</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>実機。LINE 上で実際に予約を行い、文字入力を要しないことを確認</t>
+          <t>自動テスト（会話）</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1537,7 +1521,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="26" customHeight="1">
       <c r="A22" s="10" t="n">
         <v>19</v>
       </c>
@@ -1548,12 +1532,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>選択肢が画面に正しく表示されること</t>
+          <t>空き状況が3状態（予約済み／予約不可／空き）で表示されること</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>実機（V-4）。18件の時刻ボタンと12室の一覧の表示崩れを確認</t>
+          <t>自動テスト（会話）</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -1562,7 +1546,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" ht="26" customHeight="1">
       <c r="A23" s="12" t="n">
         <v>20</v>
       </c>
@@ -1573,12 +1557,12 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>想定外の入力に無言で終わらないこと</t>
+          <t>登録情報の変更が既存の予約に反映されること</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。解釈できない文字列に対して案内が返ることを確認</t>
+          <t>自動テスト（会話）</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
@@ -1587,23 +1571,23 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="n">
         <v>21</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>他人の予約を変更・キャンセルできないこと</t>
+          <t>日時・時間・部屋の指定がすべてボタン操作で完結すること</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。ボタン非表示だけでなく、処理側での拒否を確認</t>
+          <t>実機</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -1612,23 +1596,23 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
+    <row r="25" ht="26" customHeight="1">
       <c r="A25" s="12" t="n">
         <v>22</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>シートへの直接入力が予約として取り込まれること</t>
+          <t>選択肢が画面に正しく表示されること</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。管理者の編集を再現し、採番・同期・履歴を確認</t>
+          <t>実機（V-4）</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -1637,23 +1621,23 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="26" ht="26" customHeight="1">
       <c r="A26" s="10" t="n">
         <v>23</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>入力途中の行が誤って取り込まれないこと</t>
+          <t>想定外の入力に無言で終わらないこと</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。必須4項目が揃うまで処理されないことを確認</t>
+          <t>自動テスト（会話）</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -1662,23 +1646,23 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" ht="26" customHeight="1">
       <c r="A27" s="12" t="n">
         <v>24</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>不正な入力が警告として通知されること</t>
+          <t>他人の予約を変更・キャンセルできないこと</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。二重予約・定員超過・部屋名不一致など7種を確認</t>
+          <t>自動テスト（予約・会話）</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -1687,7 +1671,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
+    <row r="28" ht="26" customHeight="1">
       <c r="A28" s="10" t="n">
         <v>25</v>
       </c>
@@ -1698,12 +1682,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>管理者の編集が拒否されないこと</t>
+          <t>シートへの直接入力が予約として取り込まれること</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。警告は出すが値の書き換えや拒否をしないことを確認</t>
+          <t>自動テスト（シート編集）</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -1712,7 +1696,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
+    <row r="29" ht="26" customHeight="1">
       <c r="A29" s="12" t="n">
         <v>26</v>
       </c>
@@ -1723,12 +1707,12 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>管理者は受付締切の制約を受けないこと</t>
+          <t>入力途中の行が誤って取り込まれないこと</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。過去日付の代理予約が登録できることを確認</t>
+          <t>自動テスト（シート編集）</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -1737,7 +1721,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
+    <row r="30" ht="26" customHeight="1">
       <c r="A30" s="10" t="n">
         <v>27</v>
       </c>
@@ -1748,12 +1732,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>操作履歴が記録されること</t>
+          <t>不正な入力が警告として通知されること</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。作成・変更・キャンセルと実施者の記録を確認</t>
+          <t>自動テスト（シート編集）</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -1762,23 +1746,23 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
+    <row r="31" ht="26" customHeight="1">
       <c r="A31" s="12" t="n">
         <v>28</v>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>予約・変更・キャンセルのメールが届くこと</t>
+          <t>管理者の編集が拒否・書き換えされないこと</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>実機。実際に送信し受信を確認</t>
+          <t>自動テスト（シート編集）</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1787,23 +1771,23 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="26" customHeight="1">
       <c r="A32" s="10" t="n">
         <v>29</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>カレンダー登録用ファイルが正しい形式であること</t>
+          <t>管理者は受付締切の制約を受けないこと</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。規格（RFC 5545）への適合を項目単位で確認</t>
+          <t>自動テスト（シート編集）</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -1812,23 +1796,23 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
+    <row r="33" ht="26" customHeight="1">
       <c r="A33" s="12" t="n">
         <v>30</v>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>添付を開くと個人カレンダーに登録されること</t>
+          <t>操作履歴が実施者とともに記録されること</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>実機（V-7）。Google／Outlook の両方で確認</t>
+          <t>自動テスト（シート編集）</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -1837,7 +1821,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
+    <row r="34" ht="26" customHeight="1">
       <c r="A34" s="10" t="n">
         <v>31</v>
       </c>
@@ -1848,12 +1832,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>変更・キャンセルが個人カレンダーに自動反映されること</t>
+          <t>予約・変更・キャンセルのメールが届くこと</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>実機（V-7）。予定が重複せず、最後に削除されることを目視で確認</t>
+          <t>実機</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -1862,7 +1846,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
+    <row r="35" ht="26" customHeight="1">
       <c r="A35" s="12" t="n">
         <v>32</v>
       </c>
@@ -1873,12 +1857,12 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>カレンダー追加リンクが正しく開くこと</t>
+          <t>カレンダー登録用ファイルが規格に適合すること</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>実機（V-5）。外部ブラウザでの起動と日時のずれがないことを確認</t>
+          <t>自動テスト（通知）</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -1887,7 +1871,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
+    <row r="36" ht="26" customHeight="1">
       <c r="A36" s="10" t="n">
         <v>33</v>
       </c>
@@ -1898,12 +1882,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>メールアドレス未登録の予約で処理が止まらないこと</t>
+          <t>添付を開くと個人カレンダーに登録されること</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。通知を省略し予約自体は成立することを確認</t>
+          <t>実機（V-7）</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -1912,7 +1896,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
+    <row r="37" ht="26" customHeight="1">
       <c r="A37" s="12" t="n">
         <v>34</v>
       </c>
@@ -1923,12 +1907,12 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>通知の失敗が予約の成立に影響しないこと</t>
+          <t>変更・キャンセルが個人カレンダーに自動反映されること</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。送信失敗時も予約が成立することを確認</t>
+          <t>実機（V-7）</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -1937,23 +1921,23 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1">
+    <row r="38" ht="26" customHeight="1">
       <c r="A38" s="10" t="n">
         <v>35</v>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>共有カレンダーに予約が反映されること</t>
+          <t>カレンダー追加リンクが正しく開くこと</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>実機（V-6）。作成・更新・削除の3操作を確認</t>
+          <t>実機（V-5）</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -1962,23 +1946,23 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
+    <row r="39" ht="26" customHeight="1">
       <c r="A39" s="12" t="n">
         <v>36</v>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>同期の失敗が記録され、管理者が気づけること</t>
+          <t>メールアドレス未登録の予約で処理が止まらないこと</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。警告列への記録と管理者への障害通知を確認</t>
+          <t>自動テスト（通知）</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -1987,23 +1971,23 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
+    <row r="40" ht="26" customHeight="1">
       <c r="A40" s="10" t="n">
         <v>37</v>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>日付・時刻が文字列として保持されること</t>
+          <t>通知の失敗が予約の成立に影響しないこと</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>自動診断。全シートの列書式と保存値の型を検査</t>
+          <t>自動テスト（通知）</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -2012,23 +1996,23 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
+    <row r="41" ht="26" customHeight="1">
       <c r="A41" s="12" t="n">
         <v>38</v>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>タイムゾーンが日本時間に統一されていること</t>
+          <t>共有カレンダーに予約が反映されること</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>自動診断。スクリプトとスプレッドシートの両方を検査</t>
+          <t>実機（V-6）</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -2037,23 +2021,23 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
+    <row r="42" ht="26" customHeight="1">
       <c r="A42" s="10" t="n">
         <v>39</v>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>時刻の比較・加算が正しく行われること</t>
+          <t>同期の失敗が記録され、管理者が気づけること</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。境界値と表記ゆれを含めて確認</t>
+          <t>自動テスト（予約）</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -2062,7 +2046,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
+    <row r="43" ht="26" customHeight="1">
       <c r="A43" s="12" t="n">
         <v>40</v>
       </c>
@@ -2073,12 +2057,12 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>設定値が正しく読み込まれること</t>
+          <t>日付・時刻が文字列として保持されること</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>自動診断。全項目の値と、不正値時の既定値動作を検査</t>
+          <t>自動診断</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -2087,7 +2071,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
+    <row r="44" ht="26" customHeight="1">
       <c r="A44" s="10" t="n">
         <v>41</v>
       </c>
@@ -2098,12 +2082,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>マスタデータが想定どおり読めること</t>
+          <t>タイムゾーンが日本時間に統一されていること</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>自動診断。部屋数・定員・営業時間を検査</t>
+          <t>自動診断</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -2112,23 +2096,23 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
+    <row r="45" ht="26" customHeight="1">
       <c r="A45" s="12" t="n">
         <v>42</v>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>古いメッセージのボタンが押されても矛盾しないこと</t>
+          <t>時刻の比較・加算が正しく行われること</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>自動テスト。確定時に再判定が行われることを確認</t>
+          <t>自動テスト（空き判定）</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -2137,23 +2121,23 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
+    <row r="46" ht="26" customHeight="1">
       <c r="A46" s="10" t="n">
         <v>43</v>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>通信の重複で予約が2件成立しないこと</t>
+          <t>設定値が正しく読み込まれること</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>自動テスト。同一イベントの再送が無視されることを確認</t>
+          <t>自動診断</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -2162,23 +2146,23 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
+    <row r="47" ht="26" customHeight="1">
       <c r="A47" s="12" t="n">
         <v>44</v>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Webhook がエラーで停止しないこと</t>
+          <t>マスタデータが想定どおり読めること</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>実機（V-1〜V-3）。空リクエスト・不正トークンでの動作を確認</t>
+          <t>自動診断</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2187,41 +2171,16 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>例外発生時に利用者へ案内が返ること</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>自動テスト。処理失敗時の応答を確認</t>
-        </is>
-      </c>
-      <c r="E48" s="11" t="inlineStr">
-        <is>
-          <t>合格</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="14" t="inlineStr"/>
-      <c r="B49" s="14" t="inlineStr"/>
-      <c r="C49" s="14" t="inlineStr">
-        <is>
-          <t>合計 45 項目</t>
-        </is>
-      </c>
-      <c r="D49" s="14" t="inlineStr"/>
-      <c r="E49" s="16" t="inlineStr">
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="14" t="inlineStr"/>
+      <c r="B48" s="14" t="inlineStr"/>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>合計 44 項目</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr"/>
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>全項目合格</t>
         </is>
@@ -2233,7 +2192,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2243,311 +2202,281 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col hidden="1" width="6" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>検出事項と対処</t>
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>検証の観点【異常系】— 運用上のリスクに耐えるか</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>検証は不具合を見つけるために行った。以下はすべて検証の過程で検出し、対処したものである。</t>
+          <t>要件には書かれていない壊れ方が対象。「何が起きたら業務が止まるか」から観点を立てている。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr"/>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>検出した事象</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>影響度</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>対処</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr"/>
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>観点</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>なぜこの観点が必要か</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>検証項目数</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>X-A</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>改竄されたリクエストに耐えること</t>
+        </is>
+      </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>二重予約を防げない状態だった</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>重大</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>日付と時刻がシート上で自動変換され、予約が別の時刻として保存されていた。検証で「同じ枠に2件取れる」という形で表面化した。</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>値を書き込む直前に列の書式を固定する方式へ変更。自動診断でも検査するようにした。</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>修正済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr"/>
+          <t>GAS の制約で署名検証が使えず、Webhook URL が漏れれば第三者が任意の値を送れる（受容した制約）。壊れた値で処理が止まったり、意味不明な応答を返したりしてはならない。</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>X-B</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>想定外の入力で処理が止まらないこと</t>
+        </is>
+      </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>変更・キャンセルの通知が届かない可能性があった</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>重大</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>カレンダー登録用ファイルが規格の行長制限に違反していた。厳格に解釈する環境ではファイルごと無視される。</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>規格どおりに折り返す処理を実装。招待として扱われるための指定も追加した。</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>修正済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr"/>
+          <t>空白のみ、極端に長い文字列、絵文字などは、悪意がなくても日常的に送られる。1人の入力でBotが応答不能になると、影響は全社に及ぶ。</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>X-C</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>想定外のイベントで落ちないこと</t>
+        </is>
+      </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>管理者への警告が消えることがあった</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>検証結果とカレンダー同期の失敗が同じ欄を奪い合い、後から書いた側が相手の内容を消していた。管理者が異常に気づけない。</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>書き込み処理を1箇所に集約した。</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>修正済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr"/>
+          <t>スタンプ・画像・グループ招待・友だち解除など、こちらが想定していないイベントは必ず届く。LINE 側の仕様追加でも新しい種別が増える。</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>X-D</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>通信の異常で二重処理しないこと</t>
+        </is>
+      </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>時刻の変更（短縮）ができなかった</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>変更時に自分自身の予約を判定から除外しておらず、いま押さえている時刻が選択肢から消えていた。</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>選択肢の生成側にも除外処理を通した。</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>修正済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr"/>
+          <t>LINE は応答が遅いと同じイベントを再送する。排他制御では防げないため、1回の操作が2件の予約になりうる。</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>X-E</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>データが壊れていても判定が続くこと</t>
+        </is>
+      </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>「本日の予約」が常に空表示になる状態だった</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>スプレッドシートのタイムゾーンが日本時間になっておらず、当日判定が別の日を指していた。</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>タイムゾーンを統一し、自動診断で検査するようにした。</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>修正済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr"/>
+          <t>管理者の手入力ミスや、入力途中の行は必ず発生する。1行の異常で全社の予約受付が止まってはならない。</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>X-F</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>境界値で判断がぶれないこと</t>
+        </is>
+      </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>予約の行を削除すると不整合が残る</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>シートの行を消すと共有カレンダーとの紐付けが失われ、カレンダー側の予定を削除できなくなる。システムでは防げない。</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>運用ルールとして管理者ガイドとシート冒頭に明記。キャンセルは状態列の変更で行う。</t>
-        </is>
-      </c>
-      <c r="G9" s="21" t="inlineStr">
-        <is>
-          <t>運用で回避</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr"/>
+          <t>営業時間ちょうど、定員ちょうど、予約可能日数ちょうど。1件だけ通る／通らないという誤りは、発見が最も遅れる種類の不具合である。</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>X-G</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>個人カレンダーへの連携が壊れないこと</t>
+        </is>
+      </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>検証が共有カレンダーに不要な予定を残していた</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>軽微</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>テスト実行のたびにカレンダーへ予定が残り、蓄積すると実際の予約と区別がつかなくなる。</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>テストの後片付けでカレンダー側も削除するようにした。</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>修正済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>重大2件はいずれも「エラーを出さずに壊れる」種類の不具合であり、通常の動作確認では発見できない。自動テストを先に用意したことで検出できた。</t>
+          <t>予約名に絵文字や記号が入ることは日常的にある。ファイルの規格を外れると、予定全体が読めず無言で失敗する。</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>X-H</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>外部サービスの失敗が予約に波及しないこと</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>カレンダーの削除、宛先不明、送信上限は運用中に必ず起きる。連携の失敗で予約そのものが不成立になってはならない。</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="18" t="inlineStr"/>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr"/>
+      <c r="D12" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>合格</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C12:G12"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2557,170 +2486,1877 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col hidden="1" width="6" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>検証項目と結果【異常系】</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>悪意の有無を問わず、実運用で起こりうる入力・状態を対象とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>観点</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>検証項目</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>検証方法</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>X-A</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>存在しない日付・時刻を送られても、読み取れない旨を返すこと</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>X-A</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>負・0・小数の利用時間や人数を拒むこと</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>X-A</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>実在しない日（2月30日など）を有効な日付として扱わないこと</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>X-A</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>未知の操作・未知の手順・空のデータで落ちないこと</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>X-A</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>存在しない部屋ID・予約IDを指定されても落ちないこと</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>X-A</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>確定処理を直接呼ばれても、手順を踏まない予約が成立しないこと</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>X-A</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>データ長の上限超過を検出できること</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>X-B</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>空白のみ・制御文字・極端に長い文字列で落ちないこと</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>X-B</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>絵文字やHTML・JSONらしき文字列で落ちないこと</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>X-B</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>氏名・メールアドレス・人数の検証が境界で正しく働くこと</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>X-B</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>入力待ちの記録が壊れていても、無言で終わらないこと</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>X-C</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>userId が取得できないイベントで落ちないこと</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>X-C</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>画像・スタンプ・未知の種別のイベントで落ちないこと</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>X-C</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>本文を欠いたイベントで落ちないこと</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>X-D</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>同一イベントの再送を検出して無視すること</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>X-D</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>壊れた本文・不正なトークンのリクエストを破棄すること</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>X-D</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>どのような入力でも LINE に正常応答を返すこと</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>X-E</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>終了が開始より前など、壊れた予約行があっても判定が続くこと</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>X-E</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>状態が未入力の行が枠を塞がないこと</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>X-E</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>定員が0・負・数値でない部屋を候補に出さないこと</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>X-E</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>営業時間の開始と終了が逆転していても予約させないこと</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>X-E</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>設定値が不正なとき既定値で動作すること</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>自動診断</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>X-F</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>時間帯の重複判定が境界で正しいこと</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>X-F</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>営業時間の開始・終了ちょうどが利用できること</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>X-F</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>時刻の上限・下限（00:00／24:00／分が60）を正しく扱うこと</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>X-F</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>予約可能日数の境界で判定が切り替わること</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>X-F</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>定員ちょうど／定員なしの部屋が正しく扱われること</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>X-G</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>絵文字を含む予約名でファイルが壊れないこと</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>X-G</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>区切り文字（カンマ・セミコロン・改行）が行を壊さないこと</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>X-G</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>項目が空でもファイルを生成できること</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>X-H</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>存在しないカレンダー・予定を指定されても落ちないこと</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>X-H</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>削除済みの予定に再度削除を行っても落ちないこと</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>実機／自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>X-H</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>宛先が引けない予約で通知処理が止まらないこと</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>X-H</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>管理者通知先が未設定でも例外処理が落ちないこと</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="18" t="inlineStr"/>
+      <c r="B38" s="18" t="inlineStr"/>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>合計 34 項目</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr"/>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>全項目合格</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>検出事項と対処</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>検証は不具合を見つけるために行った。以下はすべて検証の過程で検出し、対処したものである。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>検出した検証</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>検出した事象</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>影響度</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>対処</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>二重予約を防げない状態だった</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>日付と時刻がシート上で自動変換され、予約が別の時刻として保存されていた。検証で「同じ枠に2件取れる」という形で表面化した。</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>値を書き込む直前に列の書式を固定する方式へ変更。自動診断でも検査する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>変更・キャンセルの通知が届かない可能性があった</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>カレンダー登録用ファイルが規格の行長制限に違反していた。厳格に解釈する環境ではファイルごと無視される。</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>規格どおりに折り返す処理を実装。招待として扱われるための指定も追加した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>異常系</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>実在しない日付が有効として扱われていた</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2月30日のような日付が形式検証を通り、曜日の判定だけが翌月の日で行われていた。改竄されたリクエストで到達できる。</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>実在する日かを往復検算して弾くようにした。閏年も正しく判定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>異常系</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>壊れた値に対して意味不明な応答を返していた</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>「9999-99-99（null）ですね」のような応答になり、利用者にはシステムが壊れたようにしか見えなかった。</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>ルーターで日付・時刻・利用時間・人数の形式を一度だけ検証するようにした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>異常系</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>本文が壊れたリクエストで例外になっていた</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>events が配列でない本文を受け取ると例外になっていた。</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>配列であることを確認してから処理するようにした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>会話の途中から抜ける手がかりが無かった</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>離脱自体は可能だったが画面に導線が無く、「この会話から出られない」と受け取られる状態だった。</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>全手順に「やめる」を追加。初回登録の途中からも抜けられるようにした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>初回登録の案内が目的と手順を伝えていなかった</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>登録が必須であること・いつ終わるのか・あとで直せるのかが伝わらず、突然の入力要求が手続きの押し付けに見えていた。</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>必須である旨・進捗（1/2）・復帰先・変更手段を明示。使い方に登録情報の変更ボタンを追加した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>管理者への警告が消えることがあった</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>検証結果とカレンダー同期の失敗が同じ欄を奪い合い、後から書いた側が相手の内容を消していた。</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>書き込み処理を1箇所に集約した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>時刻の変更（短縮）ができなかった</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>変更時に自分自身の予約を判定から除外しておらず、いま押さえている時刻が選択肢から消えていた。</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>選択肢の生成側にも除外処理を通した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>「本日の予約」が常に空表示になる状態だった</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>スプレッドシートのタイムゾーンが日本時間になっておらず、当日判定が別の日を指していた。</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>タイムゾーンを統一し、自動診断で検査するようにした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>異常系</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>削除済みのカレンダー予定への再削除で例外になっていた</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>キャンセル自体は成功しているのに警告が記録され、管理者へ障害通知まで飛んでいた。</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>既に消えていた場合は成功として扱うようにした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>運用</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>予約の行削除がカレンダーに不整合を残す</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>シートの行を消すとカレンダーとの紐付けが失われ、カレンダー側の予定を削除できなくなる。システムでは防げない。</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>運用ルールとして管理者ガイドとシート冒頭に明記。キャンセルは状態列の変更で行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>検証が共有カレンダーに不要な予定を残していた</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>軽微</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>テスト実行のたびにカレンダーへ予定が残り、実際の予約と区別がつかなくなる。</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>テストの後片付けでカレンダー側も削除するようにした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>重大2件はいずれも「エラーを出さずに壊れる」種類の不具合であり、通常の動作確認では発見できない。自動テストを先に用意したことで検出できた。異常系の検証では、要件の検証では現れない3件を新たに検出している。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>残課題</t>
+          <t>検証の再実行</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>いずれもリリース可否に影響しない。運用しながら確認・対応する。</t>
+          <t>Apps Script エディタでファイルを開き、関数を選んで実行する。仕様を変更したときは、該当する区分を再実行すること。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr"/>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>ファイル</t>
+        </is>
+      </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>実行する関数</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>区分</t>
+          <t>検証する内容</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>リリース判断への影響</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>対応時期</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="46" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr"/>
+          <t>実行時の作用</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>自動診断</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>selfcheck.gs</t>
+        </is>
+      </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>混雑時の体感速度</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>継続確認</t>
+          <t>selfCheck</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>シート構成・タイムゾーン・列書式・設定値・マスタデータの整合</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>排他制御は検証済みだが、実際に複数人が同時に操作したときの待ち時間は運用してみないと分からない。</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>なし。予約の正しさには影響しない。遅い場合は待ち時間の設定を調整する。</t>
-        </is>
-      </c>
-      <c r="G4" s="17" t="inlineStr">
-        <is>
-          <t>稼働後1か月で確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr"/>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（空き判定）</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>test_availability.gs</t>
+        </is>
+      </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>カレンダー追加リンクの仕様変更</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>継続確認</t>
+          <t>testAvailability</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>営業時間・定例枠・臨時ブロック・定員・締切・選択肢の生成</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Google／Outlook 側の都合で URL の仕様が変わる可能性がある。</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>なし。メール添付が主手段であり、リンクは補助手段。</t>
-        </is>
-      </c>
-      <c r="G5" s="19" t="inlineStr">
-        <is>
-          <t>不具合が出た時点で対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr"/>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（予約）</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>test_reservation.gs</t>
+        </is>
+      </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>削除された予定の自動掃除</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>未実装</t>
+          <t>testReservation</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>予約の作成・変更・キャンセル、排他制御、操作履歴</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>管理者が誤って行を削除した場合、共有カレンダーに予定が残る。現在は運用ルールで回避している。</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>なし。運用ルールで回避可能。</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>実際に発生し、蓄積が問題になった場合</t>
+          <t>シートへ書き込み、最後に削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（通知）</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>test_notify.gs</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>testNotify</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>メール文面、カレンダー登録用ファイルの規格適合、追加リンク</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（会話）</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>test_line.gs</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>testLine</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>初回登録から予約・変更・キャンセル・離脱までの会話全体</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>シートへ書き込み、最後に削除。ダミー宛にメール3通</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>自動テスト（シート編集）</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>test_admin.gs</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>testAdminEdit</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>管理者の直接編集の取り込み、採番、検証と警告</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>シートへ書き込み、最後に削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>自動テスト（異常系）</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>test_abnormal.gs</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>testAbnormal</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>改竄・想定外入力・壊れたデータ・境界値・外部連携の失敗</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>実機検証</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>verifyNotifyLive ほか</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Webhook の疎通、画面表示、カレンダー連携、.ics の取り込み</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>カレンダーとメールに作用</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>残課題</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>いずれもリリース可否に影響しない。運用しながら確認・対応する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>リリース判断への影響</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>対応時期</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>混雑時の体感速度</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>継続確認</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>排他制御は検証済みだが、複数人が同時に操作したときの待ち時間は運用してみないと分からない。</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>なし。予約の正しさには影響しない。</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>稼働後1か月で確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>カレンダー追加リンクの仕様変更</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>継続確認</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Google／Outlook 側の都合で URL の仕様が変わる可能性がある。</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>なし。メール添付が主手段であり、リンクは補助手段。</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>不具合が出た時点で対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>削除された予定の自動掃除</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>未実装</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>管理者が誤って行を削除した場合、共有カレンダーに予定が残る。現在は運用ルールで回避している。</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>なし。運用ルールで回避可能。</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>実際に発生し、蓄積が問題になった場合</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>